--- a/app/services/Excel/Final_Tempelate.xlsx
+++ b/app/services/Excel/Final_Tempelate.xlsx
@@ -880,143 +880,143 @@
   </cellStyleXfs>
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1303,749 +1303,749 @@
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="21" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="21"/>
-    <col min="3" max="3" width="16.42578125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="14" style="21" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="21" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" style="21" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="21" customWidth="1"/>
-    <col min="9" max="9" width="17" style="21" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="21" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="11"/>
+    <col min="3" max="3" width="16.42578125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="17" style="11" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="19" t="s">
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11" ht="60">
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="270">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:11" ht="255">
+      <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="10">
         <v>1</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-    </row>
-    <row r="4" spans="1:11" ht="180">
-      <c r="A4" s="21" t="s">
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+    </row>
+    <row r="4" spans="1:11" ht="165">
+      <c r="A4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="19">
         <v>2</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
     </row>
     <row r="5" spans="1:11" ht="409.5">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="19">
         <v>3</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-    </row>
-    <row r="6" spans="1:11" ht="345">
-      <c r="A6" s="21" t="s">
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" spans="1:11" ht="330">
+      <c r="A6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="19">
         <v>4</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-    </row>
-    <row r="7" spans="1:11" ht="409.5">
-      <c r="A7" s="21" t="s">
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+    </row>
+    <row r="7" spans="1:11" ht="405">
+      <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="19">
         <v>5</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11" ht="409.5">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="19">
         <v>6</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" spans="1:11" ht="300">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="19">
         <v>7</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" spans="1:11" ht="409.5">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="19">
         <v>8</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="38" t="s">
+      <c r="H10" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="I10" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
     </row>
     <row r="11" spans="1:11" ht="90">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="19">
         <v>9</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" spans="1:11" ht="150">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="19">
         <v>10</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
     </row>
     <row r="13" spans="1:11" ht="409.5">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="19">
         <v>11</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="I13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
     </row>
     <row r="14" spans="1:11" ht="195">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="19">
         <v>12</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="I14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" spans="1:11" ht="135">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="19">
         <v>13</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-    </row>
-    <row r="16" spans="1:11" ht="135">
-      <c r="A16" s="21" t="s">
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" spans="1:11" ht="120">
+      <c r="A16" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="19">
         <v>14</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H16" s="30" t="s">
+      <c r="H16" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
     </row>
     <row r="17" spans="1:11" ht="300">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="24">
         <v>15</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="34" t="s">
+      <c r="I17" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-    </row>
-    <row r="18" spans="1:11" ht="225">
-      <c r="A18" s="21" t="s">
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" spans="1:11" ht="210">
+      <c r="A18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="24">
         <v>16</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="I18" s="34" t="s">
+      <c r="I18" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-    </row>
-    <row r="19" spans="1:11" ht="156">
-      <c r="A19" s="1" t="s">
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" spans="1:11" ht="144">
+      <c r="A19" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="41">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="43" t="s">
+      <c r="D19" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="43" t="s">
+      <c r="G19" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="21" t="s">
+      <c r="I19" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="21" t="s">
+      <c r="J19" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="K19" s="46">
+      <c r="K19" s="36">
         <v>46231</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="72">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="43" t="s">
+      <c r="A20" s="42"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I20" s="21" t="s">
+      <c r="I20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="21" t="s">
+      <c r="J20" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="192">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="43" t="s">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="43" t="s">
+      <c r="G21" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="21" t="s">
+      <c r="J21" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="K21" s="46">
+      <c r="K21" s="36">
         <v>46231</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="300">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="4">
         <v>18</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="43" t="s">
+      <c r="G22" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="369.75" customHeight="1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="7">
         <v>19</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="44" t="s">
+      <c r="E23" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="43" t="s">
+      <c r="G23" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="J23" s="21" t="s">
+      <c r="J23" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="K23" s="46">
+      <c r="K23" s="36">
         <v>46205</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="252">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="45">
+      <c r="B24" s="35">
         <v>20</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="G24" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J24" s="21" t="s">
+      <c r="J24" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="K24" s="46">
+      <c r="K24" s="36">
         <v>46264</v>
       </c>
     </row>
